--- a/universo/universo-alfa.xlsx
+++ b/universo/universo-alfa.xlsx
@@ -30674,7 +30674,11 @@
           <t>ES0105394003</t>
         </is>
       </c>
-      <c r="B720" t="inlineStr"/>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>TSK.MC</t>
+        </is>
+      </c>
       <c r="C720" t="inlineStr">
         <is>
           <t>STOCK</t>

--- a/universo/universo-alfa.xlsx
+++ b/universo/universo-alfa.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11974,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12940,7 @@
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13528,7 +13528,7 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14116,7 +14116,7 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15208,7 @@
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15544,7 +15544,7 @@
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15964,7 @@
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16216,7 +16216,7 @@
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -16972,7 +16972,7 @@
       </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17014,7 @@
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="H395" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17140,7 +17140,7 @@
       </c>
       <c r="H397" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="H401" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17644,7 @@
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17686,7 @@
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17896,7 +17896,7 @@
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -17980,7 +17980,7 @@
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18022,7 +18022,7 @@
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18064,7 @@
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18316,7 +18316,7 @@
       </c>
       <c r="H425" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="H426" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18568,7 @@
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18694,7 @@
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="H436" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -18988,7 +18988,7 @@
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19030,7 +19030,7 @@
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19072,7 @@
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19282,7 +19282,7 @@
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19366,7 +19366,7 @@
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19408,7 +19408,7 @@
       </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19450,7 +19450,7 @@
       </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19492,7 +19492,7 @@
       </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19534,7 @@
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19618,7 +19618,7 @@
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19660,7 +19660,7 @@
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19786,7 +19786,7 @@
       </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19828,7 +19828,7 @@
       </c>
       <c r="H461" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="H464" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20122,7 +20122,7 @@
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20206,7 +20206,7 @@
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20332,7 +20332,7 @@
       </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H474" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20626,7 +20626,7 @@
       </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20668,7 @@
       </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20710,7 +20710,7 @@
       </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="H487" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21004,7 @@
       </c>
       <c r="H489" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21046,7 +21046,7 @@
       </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="H491" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21130,7 @@
       </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21298,7 +21298,7 @@
       </c>
       <c r="H496" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21340,7 @@
       </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="H498" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="H499" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21550,7 +21550,7 @@
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21592,7 +21592,7 @@
       </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="H504" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21760,7 +21760,7 @@
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21844,7 +21844,7 @@
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21928,7 @@
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -21970,7 +21970,7 @@
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22012,7 +22012,7 @@
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22054,7 +22054,7 @@
       </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22096,7 +22096,7 @@
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22222,7 +22222,7 @@
       </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22264,7 +22264,7 @@
       </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22306,7 +22306,7 @@
       </c>
       <c r="H520" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22390,7 +22390,7 @@
       </c>
       <c r="H522" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="H524" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22516,7 +22516,7 @@
       </c>
       <c r="H525" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22558,7 +22558,7 @@
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22600,7 +22600,7 @@
       </c>
       <c r="H527" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22642,7 +22642,7 @@
       </c>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22726,7 +22726,7 @@
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22768,7 @@
       </c>
       <c r="H531" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22810,7 +22810,7 @@
       </c>
       <c r="H532" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22894,7 +22894,7 @@
       </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="H538" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23104,7 +23104,7 @@
       </c>
       <c r="H539" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="H540" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="H541" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="H542" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="H543" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23314,7 +23314,7 @@
       </c>
       <c r="H544" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23356,7 +23356,7 @@
       </c>
       <c r="H545" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="H546" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23440,7 @@
       </c>
       <c r="H547" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23482,7 +23482,7 @@
       </c>
       <c r="H548" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23524,7 +23524,7 @@
       </c>
       <c r="H549" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23566,7 +23566,7 @@
       </c>
       <c r="H550" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23608,7 +23608,7 @@
       </c>
       <c r="H551" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="H552" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="H553" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="H554" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="H558" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="H559" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="H560" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24028,7 +24028,7 @@
       </c>
       <c r="H561" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24070,7 +24070,7 @@
       </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24112,7 +24112,7 @@
       </c>
       <c r="H563" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24154,7 +24154,7 @@
       </c>
       <c r="H564" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="H565" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="H566" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="H567" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24322,7 @@
       </c>
       <c r="H568" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="H569" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24406,7 +24406,7 @@
       </c>
       <c r="H570" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24448,7 +24448,7 @@
       </c>
       <c r="H571" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="H572" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="H573" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24574,7 +24574,7 @@
       </c>
       <c r="H574" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
       </c>
       <c r="H575" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24658,7 +24658,7 @@
       </c>
       <c r="H576" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="H577" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24742,7 +24742,7 @@
       </c>
       <c r="H578" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24784,7 +24784,7 @@
       </c>
       <c r="H579" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24826,7 +24826,7 @@
       </c>
       <c r="H580" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24952,7 +24952,7 @@
       </c>
       <c r="H583" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -24994,7 +24994,7 @@
       </c>
       <c r="H584" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25036,7 +25036,7 @@
       </c>
       <c r="H585" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="H586" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="H587" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25162,7 +25162,7 @@
       </c>
       <c r="H588" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25204,7 +25204,7 @@
       </c>
       <c r="H589" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25246,7 +25246,7 @@
       </c>
       <c r="H590" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="H591" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25330,7 +25330,7 @@
       </c>
       <c r="H592" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25372,7 @@
       </c>
       <c r="H593" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25414,7 +25414,7 @@
       </c>
       <c r="H594" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="H595" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H596" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25540,7 @@
       </c>
       <c r="H597" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25582,7 +25582,7 @@
       </c>
       <c r="H598" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25624,7 +25624,7 @@
       </c>
       <c r="H599" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25666,7 +25666,7 @@
       </c>
       <c r="H600" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25708,7 +25708,7 @@
       </c>
       <c r="H601" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25792,7 +25792,7 @@
       </c>
       <c r="H603" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25834,7 +25834,7 @@
       </c>
       <c r="H604" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25876,7 +25876,7 @@
       </c>
       <c r="H605" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25918,7 +25918,7 @@
       </c>
       <c r="H606" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="H607" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="H608" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="H609" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26086,7 +26086,7 @@
       </c>
       <c r="H610" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26128,7 +26128,7 @@
       </c>
       <c r="H611" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26170,7 +26170,7 @@
       </c>
       <c r="H612" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26212,7 +26212,7 @@
       </c>
       <c r="H613" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26254,7 +26254,7 @@
       </c>
       <c r="H614" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26296,7 @@
       </c>
       <c r="H615" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26338,7 +26338,7 @@
       </c>
       <c r="H616" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="H618" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26464,7 +26464,7 @@
       </c>
       <c r="H619" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26506,7 +26506,7 @@
       </c>
       <c r="H620" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="H621" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26590,7 +26590,7 @@
       </c>
       <c r="H622" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26632,7 +26632,7 @@
       </c>
       <c r="H623" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26674,7 +26674,7 @@
       </c>
       <c r="H624" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26716,7 @@
       </c>
       <c r="H625" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26758,7 +26758,7 @@
       </c>
       <c r="H626" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26800,7 +26800,7 @@
       </c>
       <c r="H627" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26842,7 +26842,7 @@
       </c>
       <c r="H628" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26884,7 +26884,7 @@
       </c>
       <c r="H629" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="H630" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -26968,7 +26968,7 @@
       </c>
       <c r="H631" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="H635" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27178,7 +27178,7 @@
       </c>
       <c r="H636" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27220,7 +27220,7 @@
       </c>
       <c r="H637" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27262,7 +27262,7 @@
       </c>
       <c r="H638" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27304,7 +27304,7 @@
       </c>
       <c r="H639" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27346,7 +27346,7 @@
       </c>
       <c r="H640" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27388,7 +27388,7 @@
       </c>
       <c r="H641" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27430,7 +27430,7 @@
       </c>
       <c r="H642" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27472,7 +27472,7 @@
       </c>
       <c r="H643" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="H644" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="H653" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27934,7 +27934,7 @@
       </c>
       <c r="H654" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -27976,7 +27976,7 @@
       </c>
       <c r="H655" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28018,7 +28018,7 @@
       </c>
       <c r="H656" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H657" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28102,7 +28102,7 @@
       </c>
       <c r="H658" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28144,7 +28144,7 @@
       </c>
       <c r="H659" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28186,7 +28186,7 @@
       </c>
       <c r="H660" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
       </c>
       <c r="H661" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28270,7 +28270,7 @@
       </c>
       <c r="H662" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28312,7 +28312,7 @@
       </c>
       <c r="H663" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28354,7 +28354,7 @@
       </c>
       <c r="H664" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28396,7 +28396,7 @@
       </c>
       <c r="H665" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="H666" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28480,7 +28480,7 @@
       </c>
       <c r="H667" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28522,7 +28522,7 @@
       </c>
       <c r="H668" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28564,7 +28564,7 @@
       </c>
       <c r="H669" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28606,7 +28606,7 @@
       </c>
       <c r="H670" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -28648,7 +28648,7 @@
       </c>
       <c r="H671" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -30958,7 +30958,7 @@
       </c>
       <c r="H726" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
